--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>产品主代码*</t>
   </si>
@@ -33,6 +33,18 @@
   </si>
   <si>
     <t>产品名称*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -84,11 +96,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -395,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" customWidth="1"/>
@@ -406,18 +421,27 @@
     <col min="9" max="9" width="28.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/UnClaimAssetDetail.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,10 +32,6 @@
     <t>生效截止日期（yyyy-mm-dd）*</t>
   </si>
   <si>
-    <t>产品名称*</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>数据状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -45,6 +41,10 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -411,25 +411,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="3" width="8.90625" customWidth="1"/>
-    <col min="4" max="5" width="12.90625" customWidth="1"/>
-    <col min="6" max="7" width="8.90625" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" customWidth="1"/>
-    <col min="9" max="9" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="3" width="8.875" customWidth="1"/>
+    <col min="4" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="7" width="8.875" customWidth="1"/>
+    <col min="8" max="8" width="26.125" customWidth="1"/>
+    <col min="9" max="9" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -438,10 +438,10 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -454,7 +454,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -465,7 +465,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
